--- a/templates/invoice_template_direct.xlsx
+++ b/templates/invoice_template_direct.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preve\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E22A3D1-6D42-4969-A1EF-F7ACC5A67F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF9EFBC-B73D-4D32-9CA1-9E469B1F4487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -310,15 +310,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -438,21 +429,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -624,19 +600,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -650,16 +613,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -671,7 +634,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -681,23 +644,135 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -707,212 +782,90 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -937,7 +890,7 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>128057</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>14817</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1657350" cy="1447800"/>
@@ -978,7 +931,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>33867</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>51858</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1095375" cy="552450"/>
@@ -1219,7 +1172,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL997"/>
+  <dimension ref="A1:AL998"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.28515625" style="10" customWidth="1"/>
@@ -1242,1087 +1195,1082 @@
   <sheetData>
     <row r="1" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
     </row>
     <row r="2" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-    </row>
-    <row r="3" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="17"/>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AL2" s="17"/>
+    </row>
+    <row r="3" spans="1:38" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="20"/>
-      <c r="AK3" s="20"/>
-      <c r="AL3" s="20"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="17"/>
     </row>
     <row r="4" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="67" t="s">
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="73" t="s">
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="75"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="15"/>
-      <c r="AE4" s="95" t="s">
+      <c r="T4" s="75"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="W4" s="75"/>
+      <c r="X4" s="75"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AA4" s="75"/>
+      <c r="AB4" s="76"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="67"/>
+      <c r="AG4" s="67"/>
+      <c r="AH4" s="67"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67"/>
+      <c r="AK4" s="67"/>
+      <c r="AL4" s="69"/>
+    </row>
+    <row r="5" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="78"/>
+      <c r="V5" s="78"/>
+      <c r="W5" s="78"/>
+      <c r="X5" s="78"/>
+      <c r="Y5" s="78"/>
+      <c r="Z5" s="78"/>
+      <c r="AA5" s="78"/>
+      <c r="AB5" s="79"/>
+      <c r="AC5" s="64"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="95"/>
-      <c r="AH4" s="95"/>
-      <c r="AI4" s="95"/>
-      <c r="AJ4" s="95"/>
-      <c r="AK4" s="15"/>
-      <c r="AL4" s="16"/>
-    </row>
-    <row r="5" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="78"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
-      <c r="AH5" s="96"/>
-      <c r="AI5" s="96"/>
-      <c r="AJ5" s="96"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="18"/>
-    </row>
-    <row r="6" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="65"/>
+      <c r="AL5" s="68"/>
+    </row>
+    <row r="6" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="43" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="89" t="s">
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="89"/>
-      <c r="U6" s="89"/>
-      <c r="V6" s="89"/>
-      <c r="W6" s="89"/>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="89"/>
-      <c r="AA6" s="89"/>
-      <c r="AB6" s="90"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="76"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="96"/>
-      <c r="AF6" s="96"/>
-      <c r="AG6" s="96"/>
-      <c r="AH6" s="96"/>
-      <c r="AI6" s="96"/>
-      <c r="AJ6" s="96"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
       <c r="AK6" s="11"/>
-      <c r="AL6" s="13"/>
+      <c r="AL6" s="15"/>
     </row>
     <row r="7" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="89"/>
-      <c r="T7" s="89"/>
-      <c r="U7" s="89"/>
-      <c r="V7" s="89"/>
-      <c r="W7" s="89"/>
-      <c r="X7" s="89"/>
-      <c r="Y7" s="89"/>
-      <c r="Z7" s="89"/>
-      <c r="AA7" s="89"/>
-      <c r="AB7" s="90"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="78"/>
+      <c r="U7" s="78"/>
+      <c r="V7" s="78"/>
+      <c r="W7" s="78"/>
+      <c r="X7" s="78"/>
+      <c r="Y7" s="78"/>
+      <c r="Z7" s="78"/>
+      <c r="AA7" s="78"/>
+      <c r="AB7" s="79"/>
       <c r="AC7" s="12"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="96"/>
-      <c r="AF7" s="96"/>
-      <c r="AG7" s="96"/>
-      <c r="AH7" s="96"/>
-      <c r="AI7" s="96"/>
-      <c r="AJ7" s="96"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
       <c r="AK7" s="11"/>
       <c r="AL7" s="13"/>
     </row>
-    <row r="8" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="91"/>
+      <c r="D8" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="38" t="s">
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="88" t="s">
+      <c r="J8" s="92"/>
+      <c r="K8" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="88"/>
-      <c r="O8" s="35" t="s">
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="89" t="s">
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="89"/>
-      <c r="U8" s="89"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
-      <c r="Z8" s="89"/>
-      <c r="AA8" s="89"/>
-      <c r="AB8" s="90"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
+      <c r="V8" s="75"/>
+      <c r="W8" s="75"/>
+      <c r="X8" s="75"/>
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="75"/>
+      <c r="AA8" s="75"/>
+      <c r="AB8" s="76"/>
       <c r="AC8" s="12"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96"/>
-      <c r="AI8" s="96"/>
-      <c r="AJ8" s="96"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
       <c r="AK8" s="11"/>
       <c r="AL8" s="13"/>
     </row>
-    <row r="9" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="89"/>
-      <c r="T9" s="89"/>
-      <c r="U9" s="89"/>
-      <c r="V9" s="89"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="89"/>
-      <c r="Z9" s="89"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="90"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="84"/>
+      <c r="W9" s="84"/>
+      <c r="X9" s="84"/>
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="84"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="85"/>
       <c r="AC9" s="12"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="96"/>
-      <c r="AF9" s="96"/>
-      <c r="AG9" s="96"/>
-      <c r="AH9" s="96"/>
-      <c r="AI9" s="96"/>
-      <c r="AJ9" s="96"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
       <c r="AK9" s="11"/>
       <c r="AL9" s="13"/>
     </row>
     <row r="10" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="89"/>
-      <c r="T10" s="89"/>
-      <c r="U10" s="89"/>
-      <c r="V10" s="89"/>
-      <c r="W10" s="89"/>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="90"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="84"/>
+      <c r="T10" s="84"/>
+      <c r="U10" s="84"/>
+      <c r="V10" s="84"/>
+      <c r="W10" s="84"/>
+      <c r="X10" s="84"/>
+      <c r="Y10" s="84"/>
+      <c r="Z10" s="84"/>
+      <c r="AA10" s="84"/>
+      <c r="AB10" s="85"/>
       <c r="AC10" s="12"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="96"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
       <c r="AK10" s="11"/>
       <c r="AL10" s="13"/>
     </row>
     <row r="11" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="84"/>
+      <c r="T11" s="84"/>
+      <c r="U11" s="84"/>
+      <c r="V11" s="84"/>
+      <c r="W11" s="84"/>
+      <c r="X11" s="84"/>
+      <c r="Y11" s="84"/>
+      <c r="Z11" s="84"/>
+      <c r="AA11" s="84"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="12"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="11"/>
+      <c r="AL11" s="13"/>
+    </row>
+    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="87"/>
-      <c r="M11" s="87"/>
-      <c r="N11" s="87"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="89"/>
-      <c r="T11" s="89"/>
-      <c r="U11" s="89"/>
-      <c r="V11" s="89"/>
-      <c r="W11" s="89"/>
-      <c r="X11" s="89"/>
-      <c r="Y11" s="89"/>
-      <c r="Z11" s="89"/>
-      <c r="AA11" s="89"/>
-      <c r="AB11" s="90"/>
-      <c r="AC11" s="55" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="73"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="78"/>
+      <c r="U12" s="78"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="78"/>
+      <c r="X12" s="78"/>
+      <c r="Y12" s="78"/>
+      <c r="Z12" s="78"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="79"/>
+      <c r="AC12" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="AD11" s="56"/>
-      <c r="AE11" s="56"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="56"/>
-      <c r="AH11" s="56"/>
-      <c r="AI11" s="56"/>
-      <c r="AJ11" s="56"/>
-      <c r="AK11" s="56"/>
-      <c r="AL11" s="57"/>
-    </row>
-    <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
+      <c r="AD12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="36"/>
+      <c r="AH12" s="36"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="37"/>
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+    </row>
+    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-    </row>
-    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="27"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
-      <c r="AG14" s="27"/>
-      <c r="AH14" s="27"/>
-      <c r="AI14" s="27"/>
-      <c r="AJ14" s="27"/>
-      <c r="AK14" s="27"/>
-      <c r="AL14" s="27"/>
-    </row>
-    <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="63"/>
+      <c r="X14" s="63"/>
+      <c r="Y14" s="63"/>
+      <c r="Z14" s="63"/>
+      <c r="AA14" s="63"/>
+      <c r="AB14" s="63"/>
+      <c r="AC14" s="63"/>
+      <c r="AD14" s="63"/>
+      <c r="AE14" s="63"/>
+      <c r="AF14" s="63"/>
+      <c r="AG14" s="63"/>
+      <c r="AH14" s="63"/>
+      <c r="AI14" s="63"/>
+      <c r="AJ14" s="63"/>
+      <c r="AK14" s="63"/>
+      <c r="AL14" s="63"/>
+    </row>
+    <row r="15" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="45"/>
-      <c r="Z15" s="45"/>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="45"/>
-      <c r="AC15" s="45"/>
-      <c r="AD15" s="45"/>
-      <c r="AE15" s="45"/>
-      <c r="AF15" s="45"/>
-      <c r="AG15" s="45"/>
-      <c r="AH15" s="45"/>
-      <c r="AI15" s="45"/>
-      <c r="AJ15" s="45"/>
-      <c r="AK15" s="45"/>
-      <c r="AL15" s="45"/>
-    </row>
-    <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="63"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="63"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="63"/>
+      <c r="X15" s="63"/>
+      <c r="Y15" s="63"/>
+      <c r="Z15" s="63"/>
+      <c r="AA15" s="63"/>
+      <c r="AB15" s="63"/>
+      <c r="AC15" s="63"/>
+      <c r="AD15" s="63"/>
+      <c r="AE15" s="63"/>
+      <c r="AF15" s="63"/>
+      <c r="AG15" s="63"/>
+      <c r="AH15" s="63"/>
+      <c r="AI15" s="63"/>
+      <c r="AJ15" s="63"/>
+      <c r="AK15" s="63"/>
+      <c r="AL15" s="63"/>
+    </row>
+    <row r="16" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-    </row>
-    <row r="17" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="32" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="54"/>
+      <c r="AF16" s="54"/>
+      <c r="AG16" s="54"/>
+      <c r="AH16" s="54"/>
+      <c r="AI16" s="54"/>
+      <c r="AJ16" s="54"/>
+      <c r="AK16" s="54"/>
+      <c r="AL16" s="54"/>
+    </row>
+    <row r="17" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+    </row>
+    <row r="18" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
+      <c r="B18" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="94" t="s">
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
-      <c r="AC17" s="30"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="30"/>
-      <c r="AJ17" s="30"/>
-      <c r="AK17" s="30"/>
-      <c r="AL17" s="30"/>
-    </row>
-    <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-    </row>
-    <row r="19" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="32" t="s">
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="25"/>
+      <c r="AL18" s="25"/>
+    </row>
+    <row r="19" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+    </row>
+    <row r="20" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="30" t="s">
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
-      <c r="AC19" s="30"/>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="30"/>
-      <c r="AK19" s="30"/>
-      <c r="AL19" s="30"/>
-    </row>
-    <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="1"/>
-      <c r="AI20" s="1"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-    </row>
-    <row r="21" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="25"/>
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="25"/>
+      <c r="AL20" s="25"/>
+    </row>
+    <row r="21" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+    </row>
+    <row r="22" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="49" t="s">
+      <c r="C22" s="31"/>
+      <c r="D22" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="49" t="s">
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="49" t="s">
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="52" t="s">
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AA21" s="53"/>
-      <c r="AB21" s="53"/>
-      <c r="AC21" s="53"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="54"/>
-      <c r="AF21" s="40" t="s">
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AG21" s="41"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="41"/>
-      <c r="AK21" s="42"/>
-      <c r="AL21" s="1"/>
-    </row>
-    <row r="22" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="25">
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="52"/>
+      <c r="AL22" s="1"/>
+    </row>
+    <row r="23" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
+      <c r="B23" s="26">
         <v>1</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="46" t="s">
+      <c r="C23" s="27"/>
+      <c r="D23" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="37">
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="48">
         <v>1</v>
       </c>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="47" t="s">
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="X22" s="26"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="21" t="s">
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="28" t="e">
-        <f>S22*Z22</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AG22" s="26"/>
-      <c r="AH22" s="26"/>
-      <c r="AI22" s="26"/>
-      <c r="AJ22" s="26"/>
-      <c r="AK22" s="29"/>
-      <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="25">
-        <v>2</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="37">
-        <v>1</v>
-      </c>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="91" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA23" s="92"/>
-      <c r="AB23" s="92"/>
-      <c r="AC23" s="92"/>
-      <c r="AD23" s="92"/>
-      <c r="AE23" s="93"/>
-      <c r="AF23" s="28" t="e">
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="60"/>
+      <c r="AC23" s="60"/>
+      <c r="AD23" s="60"/>
+      <c r="AE23" s="61"/>
+      <c r="AF23" s="49" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="26"/>
-      <c r="AH23" s="26"/>
-      <c r="AI23" s="26"/>
-      <c r="AJ23" s="26"/>
-      <c r="AK23" s="29"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="27"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="27"/>
+      <c r="AK23" s="50"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
-      <c r="AB24" s="4"/>
-      <c r="AC24" s="4"/>
-      <c r="AD24" s="4"/>
-      <c r="AE24" s="4"/>
-      <c r="AF24" s="4"/>
-      <c r="AG24" s="4"/>
-      <c r="AH24" s="4"/>
-      <c r="AI24" s="4"/>
-      <c r="AJ24" s="4"/>
-      <c r="AK24" s="4"/>
-      <c r="AL24" s="1"/>
-    </row>
-    <row r="25" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
-      <c r="AB25" s="5"/>
-      <c r="AC25" s="5"/>
-      <c r="AD25" s="5"/>
-      <c r="AE25" s="5" t="s">
-        <v>27</v>
+    <row r="24" spans="1:38" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="26">
+        <v>2</v>
       </c>
-      <c r="AF25" s="34" t="e">
-        <f>SUM(AF22:AK23)</f>
+      <c r="C24" s="27"/>
+      <c r="D24" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="48">
+        <v>1</v>
+      </c>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="23"/>
+      <c r="AF24" s="49" t="e">
+        <f>S24*Z24</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="20"/>
-      <c r="AH25" s="20"/>
-      <c r="AI25" s="20"/>
-      <c r="AJ25" s="20"/>
-      <c r="AK25" s="20"/>
+      <c r="AG24" s="27"/>
+      <c r="AH24" s="27"/>
+      <c r="AI24" s="27"/>
+      <c r="AJ24" s="27"/>
+      <c r="AK24" s="50"/>
+      <c r="AL24" s="3"/>
+    </row>
+    <row r="25" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -2357,16 +2305,17 @@
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
-      <c r="AF26" s="34" t="s">
-        <v>29</v>
+      <c r="AF26" s="16" t="e">
+        <f>SUM(AF23:AK24)</f>
+        <v>#VALUE!</v>
       </c>
-      <c r="AG26" s="20"/>
-      <c r="AH26" s="20"/>
-      <c r="AI26" s="20"/>
-      <c r="AJ26" s="20"/>
-      <c r="AK26" s="20"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -2401,305 +2350,305 @@
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF27" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG27" s="17"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
+      <c r="AL27" s="1"/>
+    </row>
+    <row r="28" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF27" s="34" t="e">
-        <f>SUM(AF25:AK26)</f>
+      <c r="AF28" s="16" t="e">
+        <f>SUM(AF26:AK27)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="20"/>
-      <c r="AI27" s="20"/>
-      <c r="AJ27" s="20"/>
-      <c r="AK27" s="20"/>
-      <c r="AL27" s="1"/>
-    </row>
-    <row r="28" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="44" t="s">
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="1"/>
+    </row>
+    <row r="29" spans="1:38" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="44"/>
-      <c r="AE28" s="44"/>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
-      <c r="AK28" s="44"/>
-      <c r="AL28" s="44"/>
-    </row>
-    <row r="29" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="30" t="s">
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="53"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="53"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="53"/>
+      <c r="Z29" s="53"/>
+      <c r="AA29" s="53"/>
+      <c r="AB29" s="53"/>
+      <c r="AC29" s="53"/>
+      <c r="AD29" s="53"/>
+      <c r="AE29" s="53"/>
+      <c r="AF29" s="53"/>
+      <c r="AG29" s="53"/>
+      <c r="AH29" s="53"/>
+      <c r="AI29" s="53"/>
+      <c r="AJ29" s="53"/>
+      <c r="AK29" s="53"/>
+      <c r="AL29" s="53"/>
+    </row>
+    <row r="30" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
+      <c r="B30" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AH29" s="30"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="3"/>
-      <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-      <c r="AD30" s="2"/>
-      <c r="AE30" s="2"/>
-      <c r="AF30" s="2"/>
-      <c r="AG30" s="2"/>
-      <c r="AH30" s="2"/>
-      <c r="AI30" s="2"/>
-      <c r="AJ30" s="2"/>
-      <c r="AK30" s="2"/>
-      <c r="AL30" s="2"/>
-    </row>
-    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3"/>
+    </row>
+    <row r="31" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-      <c r="AH31" s="1"/>
-      <c r="AI31" s="1"/>
-      <c r="AJ31" s="1"/>
-      <c r="AK31" s="1"/>
-      <c r="AL31" s="1"/>
-    </row>
-    <row r="32" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2"/>
+      <c r="AL31" s="2"/>
+    </row>
+    <row r="32" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="6"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
-    <row r="33" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="T33" s="24"/>
-      <c r="U33" s="24"/>
-      <c r="V33" s="24"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
-      <c r="AA33" s="24"/>
-      <c r="AB33" s="24"/>
-      <c r="AC33" s="24"/>
-      <c r="AD33" s="24"/>
-      <c r="AE33" s="24"/>
-      <c r="AF33" s="24"/>
-      <c r="AG33" s="24"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6"/>
+      <c r="AE33" s="6"/>
+      <c r="AF33" s="6"/>
+      <c r="AG33" s="6"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
     </row>
-    <row r="34" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="33" t="s">
-        <v>35</v>
+      <c r="B34" s="7" t="s">
+        <v>33</v>
       </c>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="31" t="s">
-        <v>36</v>
+      <c r="C34" s="7"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="62" t="s">
+        <v>34</v>
       </c>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="62"/>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="62"/>
+      <c r="Z34" s="62"/>
+      <c r="AA34" s="62"/>
+      <c r="AB34" s="62"/>
+      <c r="AC34" s="62"/>
+      <c r="AD34" s="62"/>
+      <c r="AE34" s="62"/>
+      <c r="AF34" s="62"/>
+      <c r="AG34" s="62"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -2708,124 +2657,124 @@
     </row>
     <row r="35" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" s="47"/>
+      <c r="U35" s="47"/>
+      <c r="V35" s="47"/>
+      <c r="W35" s="47"/>
+      <c r="X35" s="47"/>
+      <c r="Y35" s="47"/>
+      <c r="Z35" s="47"/>
+      <c r="AA35" s="47"/>
+      <c r="AB35" s="47"/>
+      <c r="AC35" s="47"/>
+      <c r="AD35" s="47"/>
+      <c r="AE35" s="47"/>
+      <c r="AF35" s="47"/>
+      <c r="AG35" s="47"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
     </row>
-    <row r="36" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="7"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="24"/>
-      <c r="AE36" s="24"/>
-      <c r="AF36" s="24"/>
-      <c r="AG36" s="24"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
     </row>
-    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="33" t="s">
-        <v>35</v>
+      <c r="B37" s="7" t="s">
+        <v>37</v>
       </c>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="31"/>
-      <c r="Z37" s="31"/>
-      <c r="AA37" s="31"/>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="62"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="62"/>
+      <c r="Y37" s="62"/>
+      <c r="Z37" s="62"/>
+      <c r="AA37" s="62"/>
+      <c r="AB37" s="62"/>
+      <c r="AC37" s="62"/>
+      <c r="AD37" s="62"/>
+      <c r="AE37" s="62"/>
+      <c r="AF37" s="62"/>
+      <c r="AG37" s="62"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -2834,40 +2783,42 @@
     </row>
     <row r="38" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1" t="s">
-        <v>38</v>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="46" t="s">
+        <v>35</v>
       </c>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="T38" s="47"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="47"/>
+      <c r="W38" s="47"/>
+      <c r="X38" s="47"/>
+      <c r="Y38" s="47"/>
+      <c r="Z38" s="47"/>
+      <c r="AA38" s="47"/>
+      <c r="AB38" s="47"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="47"/>
+      <c r="AE38" s="47"/>
+      <c r="AF38" s="47"/>
+      <c r="AG38" s="47"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
@@ -2891,7 +2842,9 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
@@ -41234,60 +41187,99 @@
       <c r="AK997" s="1"/>
       <c r="AL997" s="1"/>
     </row>
+    <row r="998" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A998" s="1"/>
+      <c r="B998" s="1"/>
+      <c r="C998" s="1"/>
+      <c r="D998" s="1"/>
+      <c r="E998" s="1"/>
+      <c r="F998" s="1"/>
+      <c r="G998" s="1"/>
+      <c r="H998" s="1"/>
+      <c r="I998" s="1"/>
+      <c r="J998" s="1"/>
+      <c r="K998" s="1"/>
+      <c r="L998" s="1"/>
+      <c r="M998" s="1"/>
+      <c r="N998" s="1"/>
+      <c r="O998" s="1"/>
+      <c r="P998" s="1"/>
+      <c r="Q998" s="1"/>
+      <c r="R998" s="1"/>
+      <c r="S998" s="1"/>
+      <c r="T998" s="1"/>
+      <c r="U998" s="1"/>
+      <c r="V998" s="1"/>
+      <c r="W998" s="1"/>
+      <c r="X998" s="1"/>
+      <c r="Y998" s="1"/>
+      <c r="Z998" s="1"/>
+      <c r="AA998" s="1"/>
+      <c r="AB998" s="1"/>
+      <c r="AC998" s="1"/>
+      <c r="AD998" s="1"/>
+      <c r="AE998" s="1"/>
+      <c r="AF998" s="1"/>
+      <c r="AG998" s="1"/>
+      <c r="AH998" s="1"/>
+      <c r="AI998" s="1"/>
+      <c r="AJ998" s="1"/>
+      <c r="AK998" s="1"/>
+      <c r="AL998" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="B7:N7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B9:N10"/>
-    <mergeCell ref="B11:N11"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="S6:AB7"/>
-    <mergeCell ref="S8:AB11"/>
+  <mergeCells count="51">
+    <mergeCell ref="O8:R12"/>
     <mergeCell ref="Z23:AE23"/>
-    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="S37:AG37"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="AE4:AJ10"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="B14:AL15"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B30:AJ30"/>
+    <mergeCell ref="G20:AL20"/>
+    <mergeCell ref="S35:AG35"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="J35:Q35"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="B1:AL3"/>
     <mergeCell ref="B4:N6"/>
     <mergeCell ref="O4:R5"/>
     <mergeCell ref="S4:AB5"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="O6:R7"/>
+    <mergeCell ref="S6:AB7"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="S8:AB12"/>
+    <mergeCell ref="B9:N11"/>
+    <mergeCell ref="AC12:AL12"/>
+    <mergeCell ref="J38:Q38"/>
+    <mergeCell ref="S38:AG38"/>
+    <mergeCell ref="S24:V24"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="S23:V23"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B28:AL28"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="D23:R23"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="B1:AL3"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="B29:AL29"/>
+    <mergeCell ref="B16:AL16"/>
+    <mergeCell ref="D24:R24"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B12:N12"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="Z24:AE24"/>
+    <mergeCell ref="G18:AL18"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="W24:Y24"/>
+    <mergeCell ref="AE5:AJ11"/>
+    <mergeCell ref="D22:R22"/>
     <mergeCell ref="Z22:AE22"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:AL14"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="B29:AJ29"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="S34:AG34"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="O8:R11"/>
-    <mergeCell ref="O6:R7"/>
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="D22:R22"/>
+    <mergeCell ref="AF26:AK26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/invoice_template_direct.xlsx
+++ b/templates/invoice_template_direct.xlsx
@@ -38,19 +38,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
-    <t>{{BANK_DIRECT_NAME}}</t>
+    <t>{{БАНК}}</t>
   </si>
   <si>
     <t>БИК</t>
   </si>
   <si>
-    <t>{{BANK_DIRECT_BIK}}</t>
+    <t>{{БАНК_БИК}}</t>
   </si>
   <si>
     <t>Сч. №</t>
   </si>
   <si>
-    <t>{{BANK_DIRECT_CORR}}</t>
+    <t>{{БАНК_КОРРСЧЕТ}}</t>
   </si>
   <si>
     <t>Банк</t>
@@ -59,16 +59,16 @@
     <t>ИНН</t>
   </si>
   <si>
-    <t>{{BANK_BEN_INN}}</t>
+    <t>{{КОМПАНИЯ_ИНН_РФ}}</t>
   </si>
   <si>
     <t xml:space="preserve">КПП  </t>
   </si>
   <si>
-    <t>{{ACCOUNT_NUMBER}}</t>
+    <t>{{СЧЕТ}}</t>
   </si>
   <si>
-    <t>ОсОО "Авто Континент"</t>
+    <t>{{КОМПАНИЯ}}</t>
   </si>
   <si>
     <t>Получатель</t>
@@ -157,13 +157,13 @@
     <t>М.П.</t>
   </si>
   <si>
-    <t>{{BANK_DIRECT_KPP}}</t>
+    <t>{{КОМПАНИЯ_КПП_РФ}}</t>
   </si>
   <si>
     <t>Отсканируйте для оплаты</t>
   </si>
   <si>
-    <t>{{QR_CODE}}</t>
+    <t>{{QR}}</t>
   </si>
   <si>
     <r>
